--- a/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Min_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -414,7 +411,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>20.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -484,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -512,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -582,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>18.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -638,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -693,8 +690,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>19.3</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -722,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -736,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -904,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -946,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -960,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -974,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1030,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>18.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1058,7 +1055,7 @@
         <v>16</v>
       </c>
       <c r="D48">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1114,7 +1111,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1212,7 +1209,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>20.6</v>
+        <v>20.06</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -635,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -901,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -915,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1209,7 +1209,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>20.06</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="60" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
@@ -761,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1027,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>18</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="47" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Min_Temperature_timeseries.xlsx
@@ -761,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -915,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1027,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>18.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:4">
